--- a/r4-ELGA-AustrianPatientSummary-test-vidi/StructureDefinition-at-aps-practitionerrole.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-test-vidi/StructureDefinition-at-aps-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-19T14:03:13+00:00</t>
+    <t>2025-03-19T15:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
